--- a/Model Validations/Crew AC Matrix.xlsx
+++ b/Model Validations/Crew AC Matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important File\Crew Management\POC\Vendors\Mu Sigma\Model Output\Model Validations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important File\Crew Management\POC\Model Evaluation\Fixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990EA905-F061-421F-A80D-C3D4D175B2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5311B715-08CF-45BE-A65F-DA798C4248B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
-    <t>Crew</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -1491,6 +1488,9 @@
   </si>
   <si>
     <t>ZURA(F)</t>
+  </si>
+  <si>
+    <t>Crew code</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1646,7 @@
     <sortCondition ref="A1:A477"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{31290332-79FC-40F8-8D2E-0D16461FF2B8}" name="Crew" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{31290332-79FC-40F8-8D2E-0D16461FF2B8}" name="Crew code" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{01B7DE93-BB0E-4C72-82EB-14678986C844}" name="100" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{FAFBF236-EA29-4214-A1C8-4611ADEB731C}" name="200" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{669C4144-14B5-4C86-88FB-289C896022FA}" name="300" dataDxfId="5"/>
@@ -1926,7 +1926,7 @@
   <dimension ref="A1:I477"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -1934,36 +1934,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2015,7 +2015,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -2380,7 +2380,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="2">
         <v>1</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2">
         <v>1</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -2685,7 +2685,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2">
         <v>1</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2">
         <v>1</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="2">
         <v>1</v>
@@ -2917,7 +2917,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2">
         <v>1</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2">
         <v>1</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2">
         <v>1</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="2">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2">
         <v>1</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="2">
         <v>1</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="2">
         <v>1</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="2">
         <v>1</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2">
         <v>1</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="2">
         <v>1</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2">
         <v>1</v>
@@ -3620,7 +3620,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="2">
         <v>1</v>
@@ -3649,7 +3649,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" s="2">
         <v>1</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="2">
         <v>1</v>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" s="2">
         <v>1</v>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" s="2">
         <v>1</v>
@@ -3759,7 +3759,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" s="2">
         <v>1</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" s="2">
         <v>1</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" s="2">
         <v>1</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="2">
         <v>1</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" s="2">
         <v>1</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B71" s="2">
         <v>1</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B72" s="2">
         <v>1</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B73" s="2">
         <v>1</v>
@@ -3981,7 +3981,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="2">
         <v>1</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B75" s="2">
         <v>1</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B76" s="2">
         <v>1</v>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B77" s="2">
         <v>1</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B78" s="2">
         <v>1</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B79" s="2">
         <v>1</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B80" s="2">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B81" s="2">
         <v>1</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B82" s="2">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B83" s="2">
         <v>1</v>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B84" s="2">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B85" s="2">
         <v>1</v>
@@ -4309,7 +4309,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B86" s="2">
         <v>1</v>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B87" s="2">
         <v>1</v>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88" s="2">
         <v>1</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" s="2">
         <v>1</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B90" s="2">
         <v>1</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B91" s="2">
         <v>1</v>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B92" s="2">
         <v>1</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B93" s="2">
         <v>1</v>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B94" s="2">
         <v>1</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B95" s="2">
         <v>1</v>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B96" s="2">
         <v>1</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B97" s="2">
         <v>1</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" s="2">
         <v>1</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B99" s="2">
         <v>1</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B100" s="2">
         <v>1</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" s="2">
         <v>1</v>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B102" s="2">
         <v>1</v>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B103" s="2">
         <v>1</v>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="2">
         <v>1</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B105" s="2">
         <v>1</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B106" s="2">
         <v>1</v>
@@ -4898,7 +4898,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B107" s="2">
         <v>1</v>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B108" s="2">
         <v>1</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B109" s="2">
         <v>1</v>
@@ -4981,7 +4981,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B110" s="2">
         <v>1</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B111" s="2">
         <v>1</v>
@@ -5037,7 +5037,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B112" s="2">
         <v>1</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B113" s="2">
         <v>1</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B114" s="2">
         <v>1</v>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B115" s="2">
         <v>1</v>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B116" s="2">
         <v>1</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B117" s="2">
         <v>1</v>
@@ -5205,7 +5205,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B118" s="2">
         <v>1</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B119" s="2">
         <v>1</v>
@@ -5261,7 +5261,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B120" s="2">
         <v>1</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B121" s="2">
         <v>1</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B122" s="2">
         <v>1</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B123" s="2">
         <v>1</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B124" s="2">
         <v>1</v>
@@ -5406,7 +5406,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B125" s="2">
         <v>1</v>
@@ -5435,7 +5435,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B126" s="2">
         <v>1</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B127" s="2">
         <v>1</v>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B128" s="2">
         <v>1</v>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B129" s="2">
         <v>1</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B130" s="2">
         <v>1</v>
@@ -5566,7 +5566,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B131" s="2">
         <v>1</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B132" s="2">
         <v>1</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B133" s="2">
         <v>1</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B134" s="2">
         <v>1</v>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B135" s="2">
         <v>1</v>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B136" s="2">
         <v>1</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B137" s="2">
         <v>1</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B138" s="2">
         <v>1</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B139" s="2">
         <v>1</v>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B140" s="2">
         <v>1</v>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B141" s="2">
         <v>1</v>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B142" s="2">
         <v>1</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B143" s="2">
         <v>1</v>
@@ -5919,7 +5919,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B144" s="2">
         <v>1</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B145" s="2">
         <v>1</v>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B146" s="2">
         <v>1</v>
@@ -6000,7 +6000,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B147" s="2">
         <v>1</v>
@@ -6029,7 +6029,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B148" s="2">
         <v>1</v>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B149" s="2">
         <v>1</v>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B150" s="2">
         <v>1</v>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B151" s="2">
         <v>1</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B152" s="2">
         <v>1</v>
@@ -6166,7 +6166,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B153" s="2">
         <v>1</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B154" s="2">
         <v>1</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B155" s="2">
         <v>1</v>
@@ -6251,7 +6251,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B156" s="2">
         <v>1</v>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B157" s="2">
         <v>1</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B158" s="2">
         <v>1</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B159" s="2">
         <v>1</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B160" s="2">
         <v>1</v>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B161" s="2">
         <v>1</v>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B162" s="2">
         <v>1</v>
@@ -6448,7 +6448,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B163" s="2">
         <v>1</v>
@@ -6477,7 +6477,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B164" s="2">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B165" s="2">
         <v>1</v>
@@ -6535,7 +6535,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B166" s="2">
         <v>1</v>
@@ -6564,7 +6564,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B167" s="2">
         <v>1</v>
@@ -6591,7 +6591,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B168" s="2">
         <v>1</v>
@@ -6614,7 +6614,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B169" s="2">
         <v>1</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B170" s="2">
         <v>1</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B171" s="2">
         <v>1</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B172" s="2">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B173" s="2">
         <v>1</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B174" s="2">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B175" s="2">
         <v>1</v>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B176" s="2">
         <v>1</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B177" s="2">
         <v>1</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B178" s="2">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B179" s="2">
         <v>1</v>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B180" s="2">
         <v>1</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B181" s="2">
         <v>1</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B182" s="2">
         <v>1</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B183" s="2">
         <v>1</v>
@@ -7037,7 +7037,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B184" s="2">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B185" s="2">
         <v>1</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B186" s="2">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B187" s="2">
         <v>1</v>
@@ -7151,7 +7151,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B188" s="2">
         <v>1</v>
@@ -7180,7 +7180,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B189" s="2">
         <v>1</v>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B190" s="2">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B191" s="2">
         <v>1</v>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B192" s="2">
         <v>1</v>
@@ -7292,7 +7292,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B193" s="2">
         <v>1</v>
@@ -7321,7 +7321,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B194" s="2">
         <v>1</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B195" s="2">
         <v>1</v>
@@ -7379,7 +7379,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B196" s="2">
         <v>1</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B197" s="2">
         <v>1</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B198" s="2">
         <v>1</v>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B199" s="2">
         <v>1</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B200" s="2">
         <v>1</v>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B201" s="2">
         <v>1</v>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B202" s="2">
         <v>1</v>
@@ -7574,7 +7574,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B203" s="2">
         <v>1</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B204" s="2">
         <v>1</v>
@@ -7630,7 +7630,7 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B205" s="2">
         <v>1</v>
@@ -7659,7 +7659,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B206" s="2">
         <v>1</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B207" s="2">
         <v>1</v>
@@ -7717,7 +7717,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B208" s="2">
         <v>1</v>
@@ -7746,7 +7746,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B209" s="2">
         <v>1</v>
@@ -7773,7 +7773,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B210" s="2">
         <v>1</v>
@@ -7800,7 +7800,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B211" s="2">
         <v>1</v>
@@ -7829,7 +7829,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B212" s="2">
         <v>1</v>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B213" s="2">
         <v>1</v>
@@ -7887,7 +7887,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B214" s="2">
         <v>1</v>
@@ -7914,7 +7914,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B215" s="2">
         <v>1</v>
@@ -7941,7 +7941,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B216" s="2">
         <v>1</v>
@@ -7970,7 +7970,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B217" s="2">
         <v>1</v>
@@ -7997,7 +7997,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B218" s="2">
         <v>1</v>
@@ -8026,7 +8026,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B219" s="2">
         <v>1</v>
@@ -8053,7 +8053,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B220" s="2">
         <v>1</v>
@@ -8080,7 +8080,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B221" s="2">
         <v>1</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B222" s="2">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B223" s="2">
         <v>1</v>
@@ -8157,7 +8157,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B224" s="2">
         <v>1</v>
@@ -8184,7 +8184,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B225" s="2">
         <v>1</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B226" s="2">
         <v>1</v>
@@ -8240,7 +8240,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B227" s="2">
         <v>1</v>
@@ -8267,7 +8267,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B228" s="2">
         <v>1</v>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B229" s="2">
         <v>1</v>
@@ -8325,7 +8325,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B230" s="2">
         <v>1</v>
@@ -8352,7 +8352,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B231" s="2">
         <v>1</v>
@@ -8381,7 +8381,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B232" s="2">
         <v>1</v>
@@ -8408,7 +8408,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B233" s="2">
         <v>1</v>
@@ -8437,7 +8437,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B234" s="2">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B235" s="2">
         <v>1</v>
@@ -8495,7 +8495,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B236" s="2">
         <v>1</v>
@@ -8524,7 +8524,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B237" s="2">
         <v>1</v>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B238" s="2">
         <v>1</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B239" s="2">
         <v>1</v>
@@ -8609,7 +8609,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B240" s="2">
         <v>1</v>
@@ -8636,7 +8636,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B241" s="2">
         <v>1</v>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B242" s="2">
         <v>1</v>
@@ -8692,7 +8692,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B243" s="2">
         <v>1</v>
@@ -8717,7 +8717,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B244" s="2">
         <v>1</v>
@@ -8744,7 +8744,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B245" s="2">
         <v>1</v>
@@ -8771,7 +8771,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B246" s="2">
         <v>1</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B247" s="2">
         <v>1</v>
@@ -8821,7 +8821,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B248" s="2">
         <v>1</v>
@@ -8850,7 +8850,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B249" s="2">
         <v>1</v>
@@ -8879,7 +8879,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B250" s="2">
         <v>1</v>
@@ -8908,7 +8908,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B251" s="2">
         <v>1</v>
@@ -8937,7 +8937,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B252" s="2">
         <v>1</v>
@@ -8966,7 +8966,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B253" s="2">
         <v>1</v>
@@ -8993,7 +8993,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B254" s="2">
         <v>1</v>
@@ -9020,7 +9020,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B255" s="2">
         <v>1</v>
@@ -9049,7 +9049,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B256" s="2">
         <v>1</v>
@@ -9072,7 +9072,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B257" s="2">
         <v>1</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B258" s="2">
         <v>1</v>
@@ -9130,7 +9130,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B259" s="2">
         <v>1</v>
@@ -9153,7 +9153,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B260" s="2">
         <v>1</v>
@@ -9182,7 +9182,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B261" s="2">
         <v>1</v>
@@ -9205,7 +9205,7 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B262" s="2">
         <v>1</v>
@@ -9234,7 +9234,7 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B263" s="2">
         <v>1</v>
@@ -9261,7 +9261,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B264" s="2">
         <v>1</v>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B265" s="2">
         <v>1</v>
@@ -9317,7 +9317,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B266" s="2">
         <v>1</v>
@@ -9344,7 +9344,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B267" s="2">
         <v>1</v>
@@ -9371,7 +9371,7 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B268" s="2">
         <v>1</v>
@@ -9398,7 +9398,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B269" s="2">
         <v>1</v>
@@ -9425,7 +9425,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B270" s="2">
         <v>1</v>
@@ -9454,7 +9454,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B271" s="2">
         <v>1</v>
@@ -9479,7 +9479,7 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B272" s="2">
         <v>1</v>
@@ -9506,7 +9506,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B273" s="2">
         <v>1</v>
@@ -9535,7 +9535,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B274" s="2">
         <v>1</v>
@@ -9564,7 +9564,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B275" s="2">
         <v>1</v>
@@ -9591,7 +9591,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B276" s="2">
         <v>1</v>
@@ -9612,7 +9612,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B277" s="2">
         <v>1</v>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B278" s="2">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B279" s="2">
         <v>1</v>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B280" s="2">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B281" s="2">
         <v>1</v>
@@ -9755,7 +9755,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B282" s="2">
         <v>1</v>
@@ -9784,7 +9784,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B283" s="2">
         <v>1</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B284" s="2">
         <v>1</v>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B285" s="2">
         <v>1</v>
@@ -9869,7 +9869,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B286" s="2">
         <v>1</v>
@@ -9898,7 +9898,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B287" s="2">
         <v>1</v>
@@ -9927,7 +9927,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B288" s="2">
         <v>1</v>
@@ -9956,7 +9956,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B289" s="2">
         <v>1</v>
@@ -9985,7 +9985,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B290" s="2">
         <v>1</v>
@@ -10012,7 +10012,7 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B291" s="2">
         <v>1</v>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B292" s="2">
         <v>1</v>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B293" s="2">
         <v>1</v>
@@ -10095,7 +10095,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B294" s="2">
         <v>1</v>
@@ -10124,7 +10124,7 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B295" s="2">
         <v>1</v>
@@ -10153,7 +10153,7 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B296" s="2">
         <v>1</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B297" s="2">
         <v>1</v>
@@ -10211,7 +10211,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B298" s="2">
         <v>1</v>
@@ -10238,7 +10238,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B299" s="2">
         <v>1</v>
@@ -10265,7 +10265,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B300" s="2">
         <v>1</v>
@@ -10294,7 +10294,7 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B301" s="2">
         <v>1</v>
@@ -10323,7 +10323,7 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B302" s="2">
         <v>1</v>
@@ -10352,7 +10352,7 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B303" s="2">
         <v>1</v>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B304" s="2">
         <v>1</v>
@@ -10406,7 +10406,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B305" s="2">
         <v>1</v>
@@ -10435,7 +10435,7 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B306" s="2">
         <v>1</v>
@@ -10464,7 +10464,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B307" s="2">
         <v>1</v>
@@ -10491,7 +10491,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B308" s="2">
         <v>1</v>
@@ -10520,7 +10520,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B309" s="2">
         <v>1</v>
@@ -10547,7 +10547,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B310" s="2">
         <v>1</v>
@@ -10576,7 +10576,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B311" s="2">
         <v>1</v>
@@ -10603,7 +10603,7 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B312" s="2">
         <v>1</v>
@@ -10632,7 +10632,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B313" s="2">
         <v>1</v>
@@ -10661,7 +10661,7 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B314" s="2">
         <v>1</v>
@@ -10690,7 +10690,7 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B315" s="2">
         <v>1</v>
@@ -10719,7 +10719,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B316" s="2">
         <v>1</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B317" s="2">
         <v>1</v>
@@ -10777,7 +10777,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B318" s="2">
         <v>1</v>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B319" s="2">
         <v>1</v>
@@ -10835,7 +10835,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B320" s="2">
         <v>1</v>
@@ -10864,7 +10864,7 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B321" s="2">
         <v>1</v>
@@ -10893,7 +10893,7 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B322" s="2">
         <v>1</v>
@@ -10922,7 +10922,7 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B323" s="2">
         <v>1</v>
@@ -10951,7 +10951,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B324" s="2">
         <v>1</v>
@@ -10978,7 +10978,7 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B325" s="2">
         <v>1</v>
@@ -11007,7 +11007,7 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B326" s="2">
         <v>1</v>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B327" s="2">
         <v>1</v>
@@ -11063,7 +11063,7 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B328" s="2">
         <v>1</v>
@@ -11092,7 +11092,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B329" s="2">
         <v>1</v>
@@ -11121,7 +11121,7 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B330" s="2">
         <v>1</v>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B331" s="2">
         <v>1</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B332" s="2">
         <v>1</v>
@@ -11204,7 +11204,7 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B333" s="2">
         <v>1</v>
@@ -11231,7 +11231,7 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B334" s="2">
         <v>1</v>
@@ -11256,7 +11256,7 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B335" s="2">
         <v>1</v>
@@ -11285,7 +11285,7 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B336" s="2">
         <v>1</v>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B337" s="2">
         <v>1</v>
@@ -11341,7 +11341,7 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B338" s="2">
         <v>1</v>
@@ -11368,7 +11368,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B339" s="2">
         <v>1</v>
@@ -11395,7 +11395,7 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B340" s="2">
         <v>1</v>
@@ -11422,7 +11422,7 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B341" s="2">
         <v>1</v>
@@ -11449,7 +11449,7 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B342" s="2">
         <v>1</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B343" s="2">
         <v>1</v>
@@ -11505,7 +11505,7 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B344" s="2">
         <v>1</v>
@@ -11534,7 +11534,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B345" s="2">
         <v>1</v>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B346" s="2">
         <v>1</v>
@@ -11590,7 +11590,7 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B347" s="2">
         <v>1</v>
@@ -11613,7 +11613,7 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B348" s="2">
         <v>1</v>
@@ -11640,7 +11640,7 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B349" s="2">
         <v>1</v>
@@ -11667,7 +11667,7 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B350" s="2">
         <v>1</v>
@@ -11696,7 +11696,7 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B351" s="2">
         <v>1</v>
@@ -11723,7 +11723,7 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B352" s="2">
         <v>1</v>
@@ -11750,7 +11750,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B353" s="2">
         <v>1</v>
@@ -11779,7 +11779,7 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B354" s="2">
         <v>1</v>
@@ -11808,7 +11808,7 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B355" s="2">
         <v>1</v>
@@ -11835,7 +11835,7 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B356" s="2">
         <v>1</v>
@@ -11864,7 +11864,7 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B357" s="2">
         <v>1</v>
@@ -11893,7 +11893,7 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B358" s="2">
         <v>1</v>
@@ -11920,7 +11920,7 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B359" s="2">
         <v>1</v>
@@ -11949,7 +11949,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B360" s="2">
         <v>1</v>
@@ -11978,7 +11978,7 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B361" s="2">
         <v>1</v>
@@ -12007,7 +12007,7 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B362" s="2">
         <v>1</v>
@@ -12030,7 +12030,7 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B363" s="2">
         <v>1</v>
@@ -12057,7 +12057,7 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B364" s="2">
         <v>1</v>
@@ -12084,7 +12084,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B365" s="2">
         <v>1</v>
@@ -12111,7 +12111,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B366" s="2">
         <v>1</v>
@@ -12138,7 +12138,7 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B367" s="2">
         <v>1</v>
@@ -12167,7 +12167,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B368" s="2">
         <v>1</v>
@@ -12196,7 +12196,7 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B369" s="2">
         <v>1</v>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B370" s="2">
         <v>1</v>
@@ -12254,7 +12254,7 @@
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B371" s="2">
         <v>1</v>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B372" s="2">
         <v>1</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B373" s="2">
         <v>1</v>
@@ -12339,7 +12339,7 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B374" s="2">
         <v>1</v>
@@ -12368,7 +12368,7 @@
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B375" s="2">
         <v>1</v>
@@ -12397,7 +12397,7 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B376" s="2">
         <v>1</v>
@@ -12424,7 +12424,7 @@
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B377" s="2">
         <v>1</v>
@@ -12451,7 +12451,7 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B378" s="2">
         <v>1</v>
@@ -12480,7 +12480,7 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B379" s="2">
         <v>1</v>
@@ -12509,7 +12509,7 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B380" s="2">
         <v>1</v>
@@ -12538,7 +12538,7 @@
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B381" s="2">
         <v>1</v>
@@ -12567,7 +12567,7 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B382" s="2">
         <v>1</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B383" s="2">
         <v>1</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B384" s="2">
         <v>1</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B385" s="2">
         <v>1</v>
@@ -12679,7 +12679,7 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B386" s="2">
         <v>1</v>
@@ -12706,7 +12706,7 @@
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B387" s="2">
         <v>1</v>
@@ -12733,7 +12733,7 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B388" s="2">
         <v>1</v>
@@ -12762,7 +12762,7 @@
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B389" s="2">
         <v>1</v>
@@ -12789,7 +12789,7 @@
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B390" s="2">
         <v>1</v>
@@ -12816,7 +12816,7 @@
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B391" s="2">
         <v>1</v>
@@ -12845,7 +12845,7 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B392" s="2">
         <v>1</v>
@@ -12874,7 +12874,7 @@
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B393" s="2">
         <v>1</v>
@@ -12901,7 +12901,7 @@
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B394" s="2">
         <v>1</v>
@@ -12928,7 +12928,7 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B395" s="2">
         <v>1</v>
@@ -12957,7 +12957,7 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B396" s="2">
         <v>1</v>
@@ -12984,7 +12984,7 @@
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B397" s="2">
         <v>1</v>
@@ -13013,7 +13013,7 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B398" s="2">
         <v>1</v>
@@ -13042,7 +13042,7 @@
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B399" s="2">
         <v>1</v>
@@ -13071,7 +13071,7 @@
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B400" s="2">
         <v>1</v>
@@ -13098,7 +13098,7 @@
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B401" s="2">
         <v>1</v>
@@ -13121,7 +13121,7 @@
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B402" s="2">
         <v>1</v>
@@ -13150,7 +13150,7 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B403" s="2">
         <v>1</v>
@@ -13173,7 +13173,7 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B404" s="2">
         <v>1</v>
@@ -13202,7 +13202,7 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B405" s="2">
         <v>1</v>
@@ -13229,7 +13229,7 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B406" s="2">
         <v>1</v>
@@ -13256,7 +13256,7 @@
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B407" s="2">
         <v>1</v>
@@ -13283,7 +13283,7 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B408" s="2">
         <v>1</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B409" s="2">
         <v>1</v>
@@ -13339,7 +13339,7 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B410" s="2">
         <v>1</v>
@@ -13362,7 +13362,7 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B411" s="2">
         <v>1</v>
@@ -13389,7 +13389,7 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B412" s="2">
         <v>1</v>
@@ -13416,7 +13416,7 @@
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B413" s="2">
         <v>1</v>
@@ -13443,7 +13443,7 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B414" s="2">
         <v>1</v>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B415" s="2">
         <v>1</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B416" s="2">
         <v>1</v>
@@ -13528,7 +13528,7 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B417" s="2">
         <v>1</v>
@@ -13553,7 +13553,7 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B418" s="2">
         <v>1</v>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B419" s="2">
         <v>1</v>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B420" s="2">
         <v>1</v>
@@ -13640,7 +13640,7 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B421" s="2">
         <v>1</v>
@@ -13669,7 +13669,7 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B422" s="2">
         <v>1</v>
@@ -13696,7 +13696,7 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B423" s="2">
         <v>1</v>
@@ -13719,7 +13719,7 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B424" s="2">
         <v>1</v>
@@ -13748,7 +13748,7 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B425" s="2">
         <v>1</v>
@@ -13777,7 +13777,7 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B426" s="2">
         <v>1</v>
@@ -13806,7 +13806,7 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B427" s="2">
         <v>1</v>
@@ -13835,7 +13835,7 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B428" s="2">
         <v>1</v>
@@ -13864,7 +13864,7 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B429" s="2">
         <v>1</v>
@@ -13893,7 +13893,7 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B430" s="2">
         <v>1</v>
@@ -13922,7 +13922,7 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B431" s="2">
         <v>1</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B432" s="2">
         <v>1</v>
@@ -13980,7 +13980,7 @@
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B433" s="2">
         <v>1</v>
@@ -14003,7 +14003,7 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B434" s="2">
         <v>1</v>
@@ -14032,7 +14032,7 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B435" s="2">
         <v>1</v>
@@ -14059,7 +14059,7 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B436" s="2">
         <v>1</v>
@@ -14088,7 +14088,7 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B437" s="2">
         <v>1</v>
@@ -14115,7 +14115,7 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B438" s="2">
         <v>1</v>
@@ -14142,7 +14142,7 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B439" s="2">
         <v>1</v>
@@ -14167,7 +14167,7 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B440" s="2">
         <v>1</v>
@@ -14190,7 +14190,7 @@
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B441" s="2">
         <v>1</v>
@@ -14217,7 +14217,7 @@
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B442" s="2">
         <v>1</v>
@@ -14246,7 +14246,7 @@
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B443" s="2">
         <v>1</v>
@@ -14275,7 +14275,7 @@
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B444" s="2">
         <v>1</v>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B445" s="2">
         <v>1</v>
@@ -14331,7 +14331,7 @@
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B446" s="2">
         <v>1</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B447" s="2">
         <v>1</v>
@@ -14389,7 +14389,7 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B448" s="2">
         <v>1</v>
@@ -14416,7 +14416,7 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B449" s="2">
         <v>1</v>
@@ -14443,7 +14443,7 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B450" s="2">
         <v>1</v>
@@ -14472,7 +14472,7 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B451" s="2">
         <v>1</v>
@@ -14501,7 +14501,7 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B452" s="2">
         <v>1</v>
@@ -14524,7 +14524,7 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B453" s="2">
         <v>1</v>
@@ -14553,7 +14553,7 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B454" s="2">
         <v>1</v>
@@ -14580,7 +14580,7 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B455" s="2">
         <v>1</v>
@@ -14603,7 +14603,7 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B456" s="2">
         <v>1</v>
@@ -14630,7 +14630,7 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B457" s="2">
         <v>1</v>
@@ -14659,7 +14659,7 @@
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B458" s="2">
         <v>1</v>
@@ -14688,7 +14688,7 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B459" s="2">
         <v>1</v>
@@ -14717,7 +14717,7 @@
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B460" s="2">
         <v>1</v>
@@ -14746,7 +14746,7 @@
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B461" s="2">
         <v>1</v>
@@ -14775,7 +14775,7 @@
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B462" s="2">
         <v>1</v>
@@ -14804,7 +14804,7 @@
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B463" s="2">
         <v>1</v>
@@ -14833,7 +14833,7 @@
     </row>
     <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B464" s="2">
         <v>1</v>
@@ -14862,7 +14862,7 @@
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B465" s="2">
         <v>1</v>
@@ -14889,7 +14889,7 @@
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B466" s="2">
         <v>1</v>
@@ -14912,7 +14912,7 @@
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B467" s="2">
         <v>1</v>
@@ -14939,7 +14939,7 @@
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B468" s="2">
         <v>1</v>
@@ -14966,7 +14966,7 @@
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B469" s="2">
         <v>1</v>
@@ -14995,7 +14995,7 @@
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B470" s="2">
         <v>1</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B471" s="2">
         <v>1</v>
@@ -15047,7 +15047,7 @@
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B472" s="2">
         <v>1</v>
@@ -15074,7 +15074,7 @@
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B473" s="2">
         <v>1</v>
@@ -15103,7 +15103,7 @@
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B474" s="2">
         <v>1</v>
@@ -15126,7 +15126,7 @@
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B475" s="2">
         <v>1</v>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B476" s="2">
         <v>1</v>
@@ -15178,7 +15178,7 @@
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B477" s="2">
         <v>1</v>
